--- a/Unity/Assets/Config/Excel/NumericConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NumericConfig.xlsx
@@ -413,329 +413,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F16"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MaxValue</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>DefaultValue</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cs</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cs</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>cs</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>属性类型ID</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>属性类型ID</t>
+          <t>属性名称</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>属性名称</t>
+          <t>最大值上限</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>最大值上限</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>默认值</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MaxValue</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DefaultValue</t>
-        </is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>99999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>99999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1000</v>
       </c>
       <c r="E6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>99999</v>
       </c>
-      <c r="F6" t="n">
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>1011</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>99999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MaxHp</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CritDmg</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HitRate</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>100</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1010</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1011</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1012</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CritRate</t>
-        </is>
       </c>
       <c r="E11" t="n">
         <v>100</v>
       </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1013</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CritDmg</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1015</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DodgeRate</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>500</v>
-      </c>
-      <c r="F12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1014</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HitRate</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1016</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>99999</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1015</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DodgeRate</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1020</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>999</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1016</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F15" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1020</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Lv</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>999</v>
-      </c>
-      <c r="F16" t="n">
         <v>1</v>
       </c>
     </row>
